--- a/Configs/GameConfig/Datas/LevelGeometry.xlsx
+++ b/Configs/GameConfig/Datas/LevelGeometry.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LevelGeometry" sheetId="1" r:id="Rdf68c5cea6254701"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LevelGeometry" sheetId="1" r:id="R0223b0a602734894"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -407,6 +407,12 @@
           <x:t xml:space="preserve">effectBinding#format=json</x:t>
         </x:is>
       </x:c>
+      <x:c r="L1" t="str">
+        <x:v>inscribedRadius</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>circumscribedRadius</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="1" t="inlineStr">
@@ -464,6 +470,12 @@
           <x:t xml:space="preserve">EffectBinding</x:t>
         </x:is>
       </x:c>
+      <x:c r="L2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>float</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1" t="inlineStr">
@@ -521,6 +533,12 @@
           <x:t xml:space="preserve">effectBinding</x:t>
         </x:is>
       </x:c>
+      <x:c r="L3" t="str">
+        <x:v>inscribedRadius</x:v>
+      </x:c>
+      <x:c r="M3" t="str">
+        <x:v>circumscribedRadius</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1" t="inlineStr">
@@ -577,6 +595,12 @@
         <x:is>
           <x:t xml:space="preserve">c</x:t>
         </x:is>
+      </x:c>
+      <x:c r="L4" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="M4" t="str">
+        <x:v>c</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -611,6 +635,12 @@
       <x:c r="K5" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":602}</x:v>
       </x:c>
+      <x:c r="L5" t="n">
+        <x:v>0.3201784340489846</x:v>
+      </x:c>
+      <x:c r="M5" t="n">
+        <x:v>0.6403568680979693</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6"/>
@@ -644,6 +674,12 @@
       <x:c r="K6" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":702}</x:v>
       </x:c>
+      <x:c r="L6" t="n">
+        <x:v>0.16100251377614153</x:v>
+      </x:c>
+      <x:c r="M6" t="n">
+        <x:v>0.32200502755228305</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7"/>
@@ -677,6 +713,12 @@
       <x:c r="K7" t="str">
         <x:v>{"$type":"TriggerProp","propPlacementId":801}</x:v>
       </x:c>
+      <x:c r="L7" t="n">
+        <x:v>0.31113983013812757</x:v>
+      </x:c>
+      <x:c r="M7" t="n">
+        <x:v>0.6222796602762549</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>
@@ -710,6 +752,12 @@
       <x:c r="K8" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":802}</x:v>
       </x:c>
+      <x:c r="L8" t="n">
+        <x:v>0.2729845109540065</x:v>
+      </x:c>
+      <x:c r="M8" t="n">
+        <x:v>0.5459690219080129</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9"/>
@@ -743,6 +791,12 @@
       <x:c r="K9" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":902}</x:v>
       </x:c>
+      <x:c r="L9" t="n">
+        <x:v>0.30282149644813683</x:v>
+      </x:c>
+      <x:c r="M9" t="n">
+        <x:v>0.6056429928962735</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10"/>
@@ -776,6 +830,12 @@
       <x:c r="K10" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":905}</x:v>
       </x:c>
+      <x:c r="L10" t="n">
+        <x:v>0.20742888954464642</x:v>
+      </x:c>
+      <x:c r="M10" t="n">
+        <x:v>0.41485777908929283</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11"/>
@@ -809,6 +869,12 @@
       <x:c r="K11" t="str">
         <x:v>{"$type":"TriggerProp","propPlacementId":1001}</x:v>
       </x:c>
+      <x:c r="L11" t="n">
+        <x:v>0.2856446701971222</x:v>
+      </x:c>
+      <x:c r="M11" t="n">
+        <x:v>0.5712893403942445</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12"/>
@@ -842,6 +908,12 @@
       <x:c r="K12" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1002}</x:v>
       </x:c>
+      <x:c r="L12" t="n">
+        <x:v>0.2632754693294927</x:v>
+      </x:c>
+      <x:c r="M12" t="n">
+        <x:v>0.5265509386589854</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13"/>
@@ -875,6 +947,12 @@
       <x:c r="K13" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1004}</x:v>
       </x:c>
+      <x:c r="L13" t="n">
+        <x:v>0.17954588429911364</x:v>
+      </x:c>
+      <x:c r="M13" t="n">
+        <x:v>0.3590917685982274</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14"/>
@@ -908,6 +986,12 @@
       <x:c r="K14" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1006}</x:v>
       </x:c>
+      <x:c r="L14" t="n">
+        <x:v>0.2841482954632754</x:v>
+      </x:c>
+      <x:c r="M14" t="n">
+        <x:v>0.5682965909265508</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15"/>
@@ -941,6 +1025,12 @@
       <x:c r="K15" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1301}</x:v>
       </x:c>
+      <x:c r="L15" t="n">
+        <x:v>0.30598960571339695</x:v>
+      </x:c>
+      <x:c r="M15" t="n">
+        <x:v>0.6119792114267939</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16"/>
@@ -974,6 +1064,12 @@
       <x:c r="K16" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1306}</x:v>
       </x:c>
+      <x:c r="L16" t="n">
+        <x:v>0.20286480231297477</x:v>
+      </x:c>
+      <x:c r="M16" t="n">
+        <x:v>0.4057296046259495</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17"/>
@@ -1007,6 +1103,12 @@
       <x:c r="K17" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1403}</x:v>
       </x:c>
+      <x:c r="L17" t="n">
+        <x:v>0.318040006366241</x:v>
+      </x:c>
+      <x:c r="M17" t="n">
+        <x:v>0.6360800127324823</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18"/>
@@ -1040,6 +1142,12 @@
       <x:c r="K18" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1404}</x:v>
       </x:c>
+      <x:c r="L18" t="n">
+        <x:v>0.1826390165559382</x:v>
+      </x:c>
+      <x:c r="M18" t="n">
+        <x:v>0.36527803311187645</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
@@ -1073,6 +1181,12 @@
       <x:c r="K19" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1502}</x:v>
       </x:c>
+      <x:c r="L19" t="n">
+        <x:v>0.3144840450563594</x:v>
+      </x:c>
+      <x:c r="M19" t="n">
+        <x:v>0.6289680901127188</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20"/>
@@ -1106,6 +1220,12 @@
       <x:c r="K20" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1504}</x:v>
       </x:c>
+      <x:c r="L20" t="n">
+        <x:v>0.20805602806083398</x:v>
+      </x:c>
+      <x:c r="M20" t="n">
+        <x:v>0.41611205612166796</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21"/>
@@ -1139,6 +1259,12 @@
       <x:c r="K21" t="str">
         <x:v>{"$type":"TriggerProp","propPlacementId":1601}</x:v>
       </x:c>
+      <x:c r="L21" t="n">
+        <x:v>0.1475082177343667</x:v>
+      </x:c>
+      <x:c r="M21" t="n">
+        <x:v>0.2950164354687334</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22"/>
@@ -1172,6 +1298,12 @@
       <x:c r="K22" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1601}</x:v>
       </x:c>
+      <x:c r="L22" t="n">
+        <x:v>0.135427612714463</x:v>
+      </x:c>
+      <x:c r="M22" t="n">
+        <x:v>0.270855225428926</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23"/>
@@ -1205,6 +1337,12 @@
       <x:c r="K23" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1606}</x:v>
       </x:c>
+      <x:c r="L23" t="n">
+        <x:v>0.14561419399180792</x:v>
+      </x:c>
+      <x:c r="M23" t="n">
+        <x:v>0.2912283879836157</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24"/>
@@ -1238,6 +1376,12 @@
       <x:c r="K24" t="str">
         <x:v>{"$type":"TriggerProp","propPlacementId":1701}</x:v>
       </x:c>
+      <x:c r="L24" t="n">
+        <x:v>0.15175211427112184</x:v>
+      </x:c>
+      <x:c r="M24" t="n">
+        <x:v>0.30350422854224374</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25"/>
@@ -1271,6 +1415,12 @@
       <x:c r="K25" t="str">
         <x:v>{"$type":"TriggerProp","propPlacementId":1702}</x:v>
       </x:c>
+      <x:c r="L25" t="n">
+        <x:v>0.12979843091585955</x:v>
+      </x:c>
+      <x:c r="M25" t="n">
+        <x:v>0.259596861831719</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26"/>
@@ -1304,6 +1454,12 @@
       <x:c r="K26" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1702}</x:v>
       </x:c>
+      <x:c r="L26" t="n">
+        <x:v>0.14999928555338066</x:v>
+      </x:c>
+      <x:c r="M26" t="n">
+        <x:v>0.29999857110676137</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27"/>
@@ -1337,6 +1493,12 @@
       <x:c r="K27" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1706}</x:v>
       </x:c>
+      <x:c r="L27" t="n">
+        <x:v>0.18703141268446433</x:v>
+      </x:c>
+      <x:c r="M27" t="n">
+        <x:v>0.37406282536892854</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28"/>
@@ -1370,6 +1532,12 @@
       <x:c r="K28" t="str">
         <x:v>{"$type":"TriggerProp","propPlacementId":1901}</x:v>
       </x:c>
+      <x:c r="L28" t="n">
+        <x:v>0.1475082177343667</x:v>
+      </x:c>
+      <x:c r="M28" t="n">
+        <x:v>0.2950164354687334</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29"/>
@@ -1403,6 +1571,12 @@
       <x:c r="K29" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1901}</x:v>
       </x:c>
+      <x:c r="L29" t="n">
+        <x:v>0.135427612714463</x:v>
+      </x:c>
+      <x:c r="M29" t="n">
+        <x:v>0.270855225428926</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30"/>
@@ -1436,6 +1610,12 @@
       <x:c r="K30" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1906}</x:v>
       </x:c>
+      <x:c r="L30" t="n">
+        <x:v>0.29122838798361583</x:v>
+      </x:c>
+      <x:c r="M30" t="n">
+        <x:v>0.5824567759672314</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31"/>
@@ -1469,6 +1649,12 @@
       <x:c r="K31" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":1903}</x:v>
       </x:c>
+      <x:c r="L31" t="n">
+        <x:v>0.20681682234815682</x:v>
+      </x:c>
+      <x:c r="M31" t="n">
+        <x:v>0.41363364469631364</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32"/>
@@ -1502,6 +1688,12 @@
       <x:c r="K32" t="str">
         <x:v>{"$type":"TriggerProp","propPlacementId":2001}</x:v>
       </x:c>
+      <x:c r="L32" t="n">
+        <x:v>0.14860035131425242</x:v>
+      </x:c>
+      <x:c r="M32" t="n">
+        <x:v>0.29720070262850495</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33"/>
@@ -1535,6 +1727,12 @@
       <x:c r="K33" t="str">
         <x:v>{"$type":"TriggerProp","propPlacementId":2002}</x:v>
       </x:c>
+      <x:c r="L33" t="n">
+        <x:v>0.12724666387309264</x:v>
+      </x:c>
+      <x:c r="M33" t="n">
+        <x:v>0.25449332774618527</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34"/>
@@ -1568,6 +1766,12 @@
       <x:c r="K34" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":2005}</x:v>
       </x:c>
+      <x:c r="L34" t="n">
+        <x:v>0.14178298998371153</x:v>
+      </x:c>
+      <x:c r="M34" t="n">
+        <x:v>0.2835659799674231</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35"/>
@@ -1601,6 +1805,12 @@
       <x:c r="K35" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":2004}</x:v>
       </x:c>
+      <x:c r="L35" t="n">
+        <x:v>0.6006858130220926</x:v>
+      </x:c>
+      <x:c r="M35" t="n">
+        <x:v>1.201371626044185</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36"/>
@@ -1634,6 +1844,12 @@
       <x:c r="K36" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":2001}</x:v>
       </x:c>
+      <x:c r="L36" t="n">
+        <x:v>0.35346506539342615</x:v>
+      </x:c>
+      <x:c r="M36" t="n">
+        <x:v>0.7069301307868524</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37"/>
@@ -1667,6 +1883,12 @@
       <x:c r="K37" t="str">
         <x:v>{"$type":"UnlockPocket","pocketPlacementId":2006}</x:v>
       </x:c>
+      <x:c r="L37" t="n">
+        <x:v>0.22662105440532718</x:v>
+      </x:c>
+      <x:c r="M37" t="n">
+        <x:v>0.4532421088106544</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
